--- a/26-2 Sports Day/예산팀/단체티 제작 업체별 견적 비교.xlsx
+++ b/26-2 Sports Day/예산팀/단체티 제작 업체별 견적 비교.xlsx
@@ -11,18 +11,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
-  <si>
-    <t>원래 디자인 장당 가격</t>
-  </si>
-  <si>
-    <t>원래 디자인 총액(150장)</t>
-  </si>
-  <si>
-    <t>HI-SIDE OUT 왼쪽가슴 장당 가격</t>
-  </si>
-  <si>
-    <t>HI-SIDE OUT 왼쪽가슴 총액(150장)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+  <si>
+    <t>옵션1 (앞뒤 모두 디자인)</t>
+  </si>
+  <si>
+    <t>옵션1 총액</t>
+  </si>
+  <si>
+    <t>옵션2 (앞쪽 HI-SIDE OUT)</t>
+  </si>
+  <si>
+    <t>옵션2 총액</t>
+  </si>
+  <si>
+    <t>옵션3 (앞쪽 캐릭터)</t>
+  </si>
+  <si>
+    <t>옵션3 총액</t>
   </si>
   <si>
     <t>인쇄 방식</t>
@@ -73,18 +79,18 @@
     <t>1,419,000원</t>
   </si>
   <si>
+    <t>9,500원</t>
+  </si>
+  <si>
+    <t>1,938,000원</t>
+  </si>
+  <si>
     <t>디지털 필름전사</t>
   </si>
   <si>
     <t>티프린스</t>
   </si>
   <si>
-    <t>14,756원</t>
-  </si>
-  <si>
-    <t>2,213,400원</t>
-  </si>
-  <si>
     <t>8,700원</t>
   </si>
   <si>
@@ -104,6 +110,12 @@
   </si>
   <si>
     <t>1,530,000원</t>
+  </si>
+  <si>
+    <t>9,200원</t>
+  </si>
+  <si>
+    <t>1,876,800원</t>
   </si>
 </sst>
 </file>
@@ -151,14 +163,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -378,193 +394,267 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="16.13"/>
-    <col customWidth="1" min="4" max="4" width="18.13"/>
-    <col customWidth="1" min="5" max="5" width="24.75"/>
-    <col customWidth="1" min="6" max="6" width="26.63"/>
+    <col customWidth="1" min="3" max="9" width="20.13"/>
   </cols>
   <sheetData>
     <row r="3">
       <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="G6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="2" t="s">
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="G8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
     </row>
     <row r="12">
+      <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
     </row>
     <row r="13">
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="14">
-      <c r="C14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
     </row>
     <row r="15">
-      <c r="C15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
     </row>
     <row r="16">
-      <c r="C16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
     </row>
     <row r="17">
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
